--- a/data/trans_orig/IP07C14-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP07C14-Edad-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de preocuparse con su aspecto en 2007 (tasa de respuesta: 89,69%)</t>
+          <t>Menores según la frecuencia de preocuparse por su aspecto en 2007 (tasa de respuesta: 89,69%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11178</t>
+          <t>10843</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>23346</t>
+          <t>23858</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>20,9%</t>
+          <t>21,36%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5353</t>
+          <t>5506</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14929</t>
+          <t>15536</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>12,72%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>18707</t>
+          <t>19053</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>34151</t>
+          <t>34595</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>14,79%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13268</t>
+          <t>13283</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>26051</t>
+          <t>25627</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>23,32%</t>
+          <t>22,94%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9608</t>
+          <t>9992</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>22017</t>
+          <t>22228</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>18,03%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>25575</t>
+          <t>26390</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>42748</t>
+          <t>43156</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>18,46%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>30759</t>
+          <t>30913</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>46802</t>
+          <t>46464</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>27,53%</t>
+          <t>27,67%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>41,9%</t>
+          <t>41,59%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>30488</t>
+          <t>30727</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>47131</t>
+          <t>47794</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>24,96%</t>
+          <t>25,16%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>38,59%</t>
+          <t>39,13%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>66282</t>
+          <t>66581</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>89091</t>
+          <t>89410</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>28,35%</t>
+          <t>28,47%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>38,1%</t>
+          <t>38,24%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8529</t>
+          <t>8305</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>20063</t>
+          <t>19362</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>17,33%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>16940</t>
+          <t>17223</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>30294</t>
+          <t>30644</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>14,1%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>25,09%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>28462</t>
+          <t>27477</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>45754</t>
+          <t>46123</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>11,75%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>19,57%</t>
+          <t>19,72%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>17627</t>
+          <t>17917</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>31878</t>
+          <t>31836</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>16,04%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>28,54%</t>
+          <t>28,5%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>27012</t>
+          <t>27457</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>43341</t>
+          <t>43165</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>22,12%</t>
+          <t>22,48%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>35,49%</t>
+          <t>35,34%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>49028</t>
+          <t>49977</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>70560</t>
+          <t>70520</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>20,97%</t>
+          <t>21,37%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>30,17%</t>
+          <t>30,16%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>36229</t>
+          <t>35600</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>55324</t>
+          <t>54859</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>19,9%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>30,92%</t>
+          <t>30,66%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>24582</t>
+          <t>25486</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>41791</t>
+          <t>41803</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>65139</t>
+          <t>65629</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>91026</t>
+          <t>91820</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>17,98%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>24,94%</t>
+          <t>25,15%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>28345</t>
+          <t>27988</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>45848</t>
+          <t>44318</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>15,84%</t>
+          <t>15,64%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>25,62%</t>
+          <t>24,77%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>23992</t>
+          <t>24152</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>39998</t>
+          <t>41015</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>12,98%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>21,49%</t>
+          <t>22,04%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>56960</t>
+          <t>57036</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>81251</t>
+          <t>82163</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>15,62%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>22,26%</t>
+          <t>22,51%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>46082</t>
+          <t>45487</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>65552</t>
+          <t>65085</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>25,75%</t>
+          <t>25,42%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>36,63%</t>
+          <t>36,37%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>44383</t>
+          <t>44020</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>64107</t>
+          <t>62642</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>23,85%</t>
+          <t>23,65%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>34,45%</t>
+          <t>33,66%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>95071</t>
+          <t>94706</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>123445</t>
+          <t>122000</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>26,04%</t>
+          <t>25,94%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>33,82%</t>
+          <t>33,42%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10776</t>
+          <t>10266</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>23129</t>
+          <t>22351</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>19442</t>
+          <t>18970</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>34545</t>
+          <t>34706</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,56%</t>
+          <t>18,65%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>33553</t>
+          <t>33130</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>53648</t>
+          <t>52092</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>14,27%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>19526</t>
+          <t>19795</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>35389</t>
+          <t>35153</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>19,78%</t>
+          <t>19,65%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>33893</t>
+          <t>33226</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>52016</t>
+          <t>51285</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18,21%</t>
+          <t>17,85%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>27,95%</t>
+          <t>27,56%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>57566</t>
+          <t>57299</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>83045</t>
+          <t>82331</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>15,7%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>22,75%</t>
+          <t>22,55%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>50273</t>
+          <t>50092</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>72323</t>
+          <t>72302</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,7 +2111,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>17,23%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>33039</t>
+          <t>33178</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>52132</t>
+          <t>52684</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>17,09%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>89260</t>
+          <t>87430</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>118651</t>
+          <t>118267</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>14,6%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>19,81%</t>
+          <t>19,75%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>45469</t>
+          <t>45697</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>66721</t>
+          <t>66560</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>15,72%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>22,96%</t>
+          <t>22,9%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>37504</t>
+          <t>37244</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>57913</t>
+          <t>57769</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>12,08%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>18,74%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>86785</t>
+          <t>88796</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>117286</t>
+          <t>117461</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>19,58%</t>
+          <t>19,61%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>82136</t>
+          <t>82497</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>107090</t>
+          <t>106066</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>28,26%</t>
+          <t>28,38%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>36,85%</t>
+          <t>36,49%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>80712</t>
+          <t>80025</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>105459</t>
+          <t>105533</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>26,19%</t>
+          <t>25,96%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>34,21%</t>
+          <t>34,24%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>169017</t>
+          <t>168323</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>206677</t>
+          <t>203814</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>28,22%</t>
+          <t>28,11%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>34,51%</t>
+          <t>34,03%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>21917</t>
+          <t>22024</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>39096</t>
+          <t>38148</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>39729</t>
+          <t>39308</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>59313</t>
+          <t>59497</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>12,75%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>19,3%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>66390</t>
+          <t>65180</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>92731</t>
+          <t>91277</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>15,24%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>41273</t>
+          <t>40856</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>61942</t>
+          <t>62037</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>14,06%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>21,31%</t>
+          <t>21,34%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>65491</t>
+          <t>65032</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>89669</t>
+          <t>89033</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>21,25%</t>
+          <t>21,1%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>29,09%</t>
+          <t>28,89%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>112950</t>
+          <t>112741</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>145094</t>
+          <t>144704</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>18,83%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>24,23%</t>
+          <t>24,16%</t>
         </is>
       </c>
     </row>
@@ -2813,7 +2813,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de preocuparse con su aspecto en 2012 (tasa de respuesta: 95,52%)</t>
+          <t>Menores según la frecuencia de preocuparse por su aspecto en 2012 (tasa de respuesta: 95,52%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3008,12 +3008,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>25914</t>
+          <t>25799</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>42698</t>
+          <t>42820</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3023,12 +3023,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>17,28%</t>
+          <t>17,2%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>28,47%</t>
+          <t>28,55%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3043,12 +3043,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>11412</t>
+          <t>11193</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>23295</t>
+          <t>23601</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>15,18%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>40221</t>
+          <t>40517</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>62253</t>
+          <t>61361</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>20,38%</t>
+          <t>20,09%</t>
         </is>
       </c>
     </row>
@@ -3121,12 +3121,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>19372</t>
+          <t>18933</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>34231</t>
+          <t>35125</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3136,12 +3136,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>12,62%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
+          <t>23,42%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3156,12 +3156,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>16351</t>
+          <t>16401</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>31056</t>
+          <t>30531</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>19,98%</t>
+          <t>19,64%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3191,12 +3191,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>39208</t>
+          <t>39713</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>61908</t>
+          <t>59268</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>19,41%</t>
         </is>
       </c>
     </row>
@@ -3234,12 +3234,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>27844</t>
+          <t>28109</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>45839</t>
+          <t>45204</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3249,12 +3249,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>18,57%</t>
+          <t>18,74%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>30,57%</t>
+          <t>30,14%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3269,12 +3269,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>33825</t>
+          <t>34254</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>53306</t>
+          <t>51866</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3284,12 +3284,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>21,76%</t>
+          <t>22,04%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>34,3%</t>
+          <t>33,37%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3304,12 +3304,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>66478</t>
+          <t>66718</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>91044</t>
+          <t>91804</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3319,12 +3319,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>21,85%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>29,81%</t>
+          <t>30,06%</t>
         </is>
       </c>
     </row>
@@ -3347,12 +3347,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15188</t>
+          <t>15245</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>28645</t>
+          <t>28854</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3362,12 +3362,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>19,1%</t>
+          <t>19,24%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3382,12 +3382,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>20423</t>
+          <t>21095</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>36839</t>
+          <t>36643</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3397,12 +3397,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>13,57%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>23,7%</t>
+          <t>23,58%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3417,12 +3417,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>40044</t>
+          <t>39372</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>60736</t>
+          <t>61548</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3432,12 +3432,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>20,15%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>24110</t>
+          <t>24606</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>39863</t>
+          <t>40477</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>16,08%</t>
+          <t>16,41%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>26,58%</t>
+          <t>26,99%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>36932</t>
+          <t>36498</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>55640</t>
+          <t>55644</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3510,7 +3510,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>23,76%</t>
+          <t>23,48%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>65837</t>
+          <t>65839</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>91481</t>
+          <t>90726</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3550,7 +3550,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>29,96%</t>
+          <t>29,71%</t>
         </is>
       </c>
     </row>
@@ -3690,12 +3690,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>35375</t>
+          <t>35406</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>54396</t>
+          <t>54771</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3705,82 +3705,82 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
+          <t>21,9%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>33,87%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>40766</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>32254</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>50911</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>23,99%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>18,98%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>29,95%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>85552</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>72575</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>97566</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>25,8%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
           <t>21,88%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>33,64%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>40766</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>33009</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>50673</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>23,99%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>19,42%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>29,81%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>123</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>85552</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>72447</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>99149</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>25,8%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>21,84%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>29,9%</t>
+          <t>29,42%</t>
         </is>
       </c>
     </row>
@@ -3803,12 +3803,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>26427</t>
+          <t>26200</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>43291</t>
+          <t>43142</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3818,12 +3818,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>26,77%</t>
+          <t>26,68%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3838,12 +3838,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>13133</t>
+          <t>13701</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>27019</t>
+          <t>27985</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3853,12 +3853,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>16,47%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>44716</t>
+          <t>45005</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>67421</t>
+          <t>67387</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3888,12 +3888,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>13,57%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>20,33%</t>
+          <t>20,32%</t>
         </is>
       </c>
     </row>
@@ -3916,12 +3916,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>36832</t>
+          <t>36323</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>56939</t>
+          <t>56229</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -3931,12 +3931,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>22,78%</t>
+          <t>22,46%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>35,22%</t>
+          <t>34,78%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -3951,12 +3951,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>43113</t>
+          <t>42474</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>62964</t>
+          <t>61876</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3966,12 +3966,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>25,37%</t>
+          <t>24,99%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>37,05%</t>
+          <t>36,41%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -3986,12 +3986,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>85037</t>
+          <t>85101</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>111473</t>
+          <t>112649</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4001,12 +4001,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>25,64%</t>
+          <t>25,66%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>33,61%</t>
+          <t>33,97%</t>
         </is>
       </c>
     </row>
@@ -4029,12 +4029,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13043</t>
+          <t>13282</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>27296</t>
+          <t>27030</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4044,12 +4044,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>16,72%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4064,12 +4064,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>22118</t>
+          <t>21741</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>38399</t>
+          <t>37664</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4079,12 +4079,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>12,79%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>22,16%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4099,12 +4099,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>39282</t>
+          <t>39342</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>59916</t>
+          <t>60388</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4114,12 +4114,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,07%</t>
+          <t>18,21%</t>
         </is>
       </c>
     </row>
@@ -4142,12 +4142,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>11498</t>
+          <t>11386</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>24062</t>
+          <t>23984</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4157,12 +4157,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4177,12 +4177,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>20889</t>
+          <t>19802</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>35218</t>
+          <t>35684</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>11,65%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>20,72%</t>
+          <t>21,0%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>34859</t>
+          <t>34853</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>55174</t>
+          <t>54088</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4232,7 +4232,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>16,31%</t>
         </is>
       </c>
     </row>
@@ -4372,12 +4372,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>66065</t>
+          <t>66021</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>90781</t>
+          <t>93830</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4387,12 +4387,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>21,18%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>29,13%</t>
+          <t>30,11%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4407,12 +4407,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>47601</t>
+          <t>47963</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>69129</t>
+          <t>70143</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4422,12 +4422,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>14,74%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>21,25%</t>
+          <t>21,56%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4442,12 +4442,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>120643</t>
+          <t>119733</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>153041</t>
+          <t>154032</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4457,12 +4457,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>24,02%</t>
+          <t>24,18%</t>
         </is>
       </c>
     </row>
@@ -4485,12 +4485,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>49377</t>
+          <t>50178</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>71865</t>
+          <t>72721</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4500,12 +4500,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>15,84%</t>
+          <t>16,1%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>23,06%</t>
+          <t>23,33%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4520,12 +4520,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>34085</t>
+          <t>34550</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>53278</t>
+          <t>54001</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4535,12 +4535,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>16,6%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4555,12 +4555,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>89329</t>
+          <t>88489</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>119170</t>
+          <t>119497</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4570,12 +4570,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>13,89%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>18,76%</t>
         </is>
       </c>
     </row>
@@ -4598,12 +4598,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>70243</t>
+          <t>70012</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>96125</t>
+          <t>96293</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4613,12 +4613,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>22,46%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>30,84%</t>
+          <t>30,9%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4633,12 +4633,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>81894</t>
+          <t>83259</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>107959</t>
+          <t>108346</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4648,12 +4648,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>25,17%</t>
+          <t>25,59%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>33,18%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>159928</t>
+          <t>159318</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>199705</t>
+          <t>194896</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4683,12 +4683,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>25,1%</t>
+          <t>25,01%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>31,35%</t>
+          <t>30,59%</t>
         </is>
       </c>
     </row>
@@ -4711,12 +4711,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>30942</t>
+          <t>31563</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>50709</t>
+          <t>51908</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -4726,12 +4726,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>16,66%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -4746,12 +4746,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>45095</t>
+          <t>45642</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>69210</t>
+          <t>68929</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -4761,12 +4761,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>14,03%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>21,27%</t>
+          <t>21,18%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -4781,12 +4781,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>84384</t>
+          <t>84170</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>114997</t>
+          <t>114899</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -4796,12 +4796,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>13,21%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>18,05%</t>
+          <t>18,04%</t>
         </is>
       </c>
     </row>
@@ -4824,12 +4824,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>39604</t>
+          <t>39197</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>60060</t>
+          <t>61487</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -4839,12 +4839,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>19,27%</t>
+          <t>19,73%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -4859,12 +4859,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>61472</t>
+          <t>61223</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>87146</t>
+          <t>85366</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>18,89%</t>
+          <t>18,82%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>26,78%</t>
+          <t>26,24%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -4894,12 +4894,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>106384</t>
+          <t>106102</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>137577</t>
+          <t>137342</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>16,66%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>21,6%</t>
+          <t>21,56%</t>
         </is>
       </c>
     </row>
@@ -5089,7 +5089,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de preocuparse con su aspecto en 2016 (tasa de respuesta: 95,57%)</t>
+          <t>Menores según la frecuencia de preocuparse por su aspecto en 2016 (tasa de respuesta: 95,57%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5284,12 +5284,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>23653</t>
+          <t>23770</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>40801</t>
+          <t>41228</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5299,12 +5299,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>22,73%</t>
+          <t>22,97%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5319,12 +5319,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>18541</t>
+          <t>18431</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>33790</t>
+          <t>33249</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5334,12 +5334,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>18,62%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5354,12 +5354,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>46801</t>
+          <t>45527</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>69062</t>
+          <t>68613</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5369,12 +5369,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>12,71%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>19,29%</t>
+          <t>19,16%</t>
         </is>
       </c>
     </row>
@@ -5397,12 +5397,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>20848</t>
+          <t>21051</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>37828</t>
+          <t>38226</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5412,12 +5412,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>21,08%</t>
+          <t>21,3%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5432,12 +5432,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>23917</t>
+          <t>23720</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>41727</t>
+          <t>41260</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5447,12 +5447,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>13,28%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>23,36%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5467,12 +5467,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>49490</t>
+          <t>49524</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>72207</t>
+          <t>74911</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5482,12 +5482,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>13,83%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>20,16%</t>
+          <t>20,92%</t>
         </is>
       </c>
     </row>
@@ -5510,12 +5510,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>36532</t>
+          <t>36468</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>55137</t>
+          <t>54172</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5525,12 +5525,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>20,36%</t>
+          <t>20,32%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>30,72%</t>
+          <t>30,18%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>26851</t>
+          <t>26809</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>43981</t>
+          <t>43257</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5560,12 +5560,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>15,01%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>24,62%</t>
+          <t>24,22%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5580,12 +5580,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>66824</t>
+          <t>67407</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>92676</t>
+          <t>93721</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5595,12 +5595,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>18,66%</t>
+          <t>18,82%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>25,88%</t>
+          <t>26,17%</t>
         </is>
       </c>
     </row>
@@ -5623,12 +5623,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>21276</t>
+          <t>22016</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>38694</t>
+          <t>38601</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5638,12 +5638,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>21,51%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5658,12 +5658,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>29262</t>
+          <t>29259</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>47862</t>
+          <t>47707</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>26,8%</t>
+          <t>26,71%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5693,12 +5693,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>55493</t>
+          <t>56025</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>80240</t>
+          <t>78716</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5708,12 +5708,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>22,41%</t>
+          <t>21,98%</t>
         </is>
       </c>
     </row>
@@ -5736,12 +5736,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>35234</t>
+          <t>35288</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>53644</t>
+          <t>53942</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5751,12 +5751,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>19,63%</t>
+          <t>19,66%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>29,89%</t>
+          <t>30,06%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5771,12 +5771,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>39841</t>
+          <t>39923</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>59918</t>
+          <t>59712</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>22,31%</t>
+          <t>22,35%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>33,55%</t>
+          <t>33,43%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>80510</t>
+          <t>80713</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>107843</t>
+          <t>109222</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>22,48%</t>
+          <t>22,54%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>30,12%</t>
+          <t>30,5%</t>
         </is>
       </c>
     </row>
@@ -5966,12 +5966,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>33887</t>
+          <t>34680</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>53100</t>
+          <t>54029</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5981,12 +5981,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>20,56%</t>
+          <t>21,04%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>32,22%</t>
+          <t>32,78%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6001,12 +6001,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>18879</t>
+          <t>18865</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>35140</t>
+          <t>35718</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6016,12 +6016,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20,6%</t>
+          <t>20,94%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6036,12 +6036,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>56507</t>
+          <t>56928</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>81014</t>
+          <t>82023</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,85%</t>
+          <t>16,97%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>24,15%</t>
+          <t>24,46%</t>
         </is>
       </c>
     </row>
@@ -6079,12 +6079,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>22570</t>
+          <t>23249</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>39078</t>
+          <t>40027</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6094,12 +6094,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>23,71%</t>
+          <t>24,29%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6114,12 +6114,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>27217</t>
+          <t>27329</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>46757</t>
+          <t>45295</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>16,02%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>27,41%</t>
+          <t>26,55%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>54879</t>
+          <t>55027</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>79839</t>
+          <t>79183</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>16,41%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>23,8%</t>
+          <t>23,61%</t>
         </is>
       </c>
     </row>
@@ -6192,12 +6192,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>38314</t>
+          <t>36024</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>58641</t>
+          <t>56672</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6207,12 +6207,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>21,86%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>35,58%</t>
+          <t>34,39%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6227,12 +6227,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>30763</t>
+          <t>32148</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>50266</t>
+          <t>50512</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18,03%</t>
+          <t>18,84%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>29,47%</t>
+          <t>29,61%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>74274</t>
+          <t>73048</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>100751</t>
+          <t>100428</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>22,14%</t>
+          <t>21,78%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>30,04%</t>
+          <t>29,94%</t>
         </is>
       </c>
     </row>
@@ -6305,12 +6305,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>16042</t>
+          <t>15239</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>30775</t>
+          <t>29951</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6320,12 +6320,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,67%</t>
+          <t>18,17%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6340,12 +6340,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>26626</t>
+          <t>26440</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>45001</t>
+          <t>45083</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6355,12 +6355,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>26,38%</t>
+          <t>26,43%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6375,12 +6375,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>45192</t>
+          <t>47037</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>69502</t>
+          <t>69911</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6390,12 +6390,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>14,02%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>20,72%</t>
+          <t>20,84%</t>
         </is>
       </c>
     </row>
@@ -6418,12 +6418,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>16315</t>
+          <t>16709</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>31147</t>
+          <t>31209</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6433,12 +6433,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>18,9%</t>
+          <t>18,94%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6453,12 +6453,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>24994</t>
+          <t>24990</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>42385</t>
+          <t>42733</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6473,7 +6473,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>24,85%</t>
+          <t>25,05%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6488,12 +6488,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>45099</t>
+          <t>44750</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>68097</t>
+          <t>68320</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6503,12 +6503,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>20,3%</t>
+          <t>20,37%</t>
         </is>
       </c>
     </row>
@@ -6648,12 +6648,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>62585</t>
+          <t>61523</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>89332</t>
+          <t>88199</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6663,12 +6663,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>18,18%</t>
+          <t>17,87%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>25,95%</t>
+          <t>25,62%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6683,12 +6683,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>40377</t>
+          <t>40935</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>63315</t>
+          <t>63405</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6698,12 +6698,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>18,13%</t>
+          <t>18,16%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6718,12 +6718,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>108022</t>
+          <t>108640</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>141653</t>
+          <t>141586</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6733,12 +6733,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>15,67%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>20,43%</t>
+          <t>20,42%</t>
         </is>
       </c>
     </row>
@@ -6761,12 +6761,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>48387</t>
+          <t>48488</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>73499</t>
+          <t>72062</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>14,05%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>21,35%</t>
+          <t>20,93%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6796,12 +6796,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>55627</t>
+          <t>56280</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>80762</t>
+          <t>81468</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6811,12 +6811,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>16,12%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>23,13%</t>
+          <t>23,33%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>110471</t>
+          <t>111458</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>143594</t>
+          <t>145195</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6846,12 +6846,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>16,07%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>20,94%</t>
         </is>
       </c>
     </row>
@@ -6874,12 +6874,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>79074</t>
+          <t>77774</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>106522</t>
+          <t>104460</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>22,97%</t>
+          <t>22,59%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>30,94%</t>
+          <t>30,34%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6909,12 +6909,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>62738</t>
+          <t>62884</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>89459</t>
+          <t>88763</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6924,12 +6924,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>18,01%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>25,62%</t>
+          <t>25,42%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>149240</t>
+          <t>148549</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>186544</t>
+          <t>184676</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6959,12 +6959,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>21,52%</t>
+          <t>21,42%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>26,9%</t>
+          <t>26,63%</t>
         </is>
       </c>
     </row>
@@ -6987,12 +6987,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>41523</t>
+          <t>40784</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>63980</t>
+          <t>62702</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>18,21%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7022,12 +7022,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>60490</t>
+          <t>60399</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>86967</t>
+          <t>85051</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7037,12 +7037,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>17,3%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>24,9%</t>
+          <t>24,36%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7057,12 +7057,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>107044</t>
+          <t>107913</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>141189</t>
+          <t>141249</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7072,12 +7072,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>15,56%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>20,36%</t>
+          <t>20,37%</t>
         </is>
       </c>
     </row>
@@ -7100,12 +7100,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>56245</t>
+          <t>57390</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>80310</t>
+          <t>80557</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>16,67%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>23,33%</t>
+          <t>23,4%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7135,12 +7135,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>69260</t>
+          <t>69703</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>96743</t>
+          <t>96024</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7150,12 +7150,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>19,83%</t>
+          <t>19,96%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>27,7%</t>
+          <t>27,5%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7170,12 +7170,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>131453</t>
+          <t>133267</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>167790</t>
+          <t>168721</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7185,12 +7185,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>18,96%</t>
+          <t>19,22%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>24,2%</t>
+          <t>24,33%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP07C14-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP07C14-Edad-trans_orig.xlsx
@@ -537,13 +537,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de preocuparse por su aspecto en 2007 (tasa de respuesta: 89,69%)</t>
+          <t>Menores según la frecuencia de preocuparse por su aspecto, percibida por el/la menor [KIDSCREEN 20] en 2007 (tasa de respuesta: 89,69%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -722,72 +722,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>9505</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>5498</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>15620</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>7,78%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>4,5%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>12,79%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>16305</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>10843</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>23858</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>10999</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>23382</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>14,6%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>9,71%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>21,36%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>9505</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>5506</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>15536</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>7,78%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>20,93%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>19053</t>
+          <t>18833</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>34595</t>
+          <t>34393</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,79%</t>
+          <t>14,71%</t>
         </is>
       </c>
     </row>
@@ -835,72 +835,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>15355</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>10058</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>21826</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>12,57%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>8,24%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>17,87%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>19061</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>13283</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>25627</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>13065</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>27005</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>17,06%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>11,89%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>22,94%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>15355</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>9992</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>22228</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>12,57%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>11,7%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>24,17%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>26390</t>
+          <t>26857</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>43156</t>
+          <t>44213</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>11,49%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>18,46%</t>
+          <t>18,91%</t>
         </is>
       </c>
     </row>
@@ -948,72 +948,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>39011</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>30791</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>47755</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>31,94%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>25,21%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>39,1%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>59</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>38859</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>30913</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>46464</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>30794</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>47005</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>34,78%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>27,67%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>41,59%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>39011</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>30727</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>47794</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>31,94%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>25,16%</t>
+          <t>27,57%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>39,13%</t>
+          <t>42,08%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>66581</t>
+          <t>66555</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>89410</t>
+          <t>89568</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>28,47%</t>
+          <t>28,46%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>38,24%</t>
+          <t>38,3%</t>
         </is>
       </c>
     </row>
@@ -1061,72 +1061,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>23079</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>16558</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>30667</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>18,9%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>13,56%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>25,11%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>13078</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>8305</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>19362</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>8736</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>19885</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>11,71%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>7,43%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>17,33%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>23079</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>17223</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>30644</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>18,9%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>25,09%</t>
+          <t>17,8%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>27477</t>
+          <t>27984</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>46123</t>
+          <t>45261</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>11,97%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>19,72%</t>
+          <t>19,36%</t>
         </is>
       </c>
     </row>
@@ -1174,72 +1174,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>35179</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>27600</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>44031</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>28,8%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>22,6%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>36,05%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>24408</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>17917</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>31836</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>18381</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>32135</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>21,85%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>16,04%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>28,5%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>35179</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>27457</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>43165</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>28,8%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>22,48%</t>
+          <t>16,45%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>35,34%</t>
+          <t>28,77%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>49977</t>
+          <t>50038</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>70520</t>
+          <t>71017</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>21,37%</t>
+          <t>21,4%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>30,16%</t>
+          <t>30,37%</t>
         </is>
       </c>
     </row>
@@ -1287,57 +1287,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>184</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>122129</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>122129</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>122129</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>168</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>111711</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>111711</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>111711</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>184</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>122129</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>122129</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>122129</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1404,72 +1404,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>32505</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>24805</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>40692</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>17,47%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>13,33%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>21,87%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>66</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>44839</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>35600</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>54859</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>36002</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>54671</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>25,06%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>19,9%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>30,66%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>32505</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>25486</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>41803</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>17,47%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>20,12%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>22,46%</t>
+          <t>30,55%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>65629</t>
+          <t>65968</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>91820</t>
+          <t>90609</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>17,98%</t>
+          <t>18,07%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>25,15%</t>
+          <t>24,82%</t>
         </is>
       </c>
     </row>
@@ -1517,72 +1517,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>31705</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>24707</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>40566</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>17,04%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>13,28%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>21,8%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>54</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>36312</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>27988</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>44318</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>28415</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>46037</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>20,29%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>15,64%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>24,77%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>31705</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>24152</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>41015</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>17,04%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>15,88%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>22,04%</t>
+          <t>25,73%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>57036</t>
+          <t>55953</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>82163</t>
+          <t>81044</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>15,62%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>22,51%</t>
+          <t>22,2%</t>
         </is>
       </c>
     </row>
@@ -1630,72 +1630,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>53373</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>43602</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>62178</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>28,68%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>23,43%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>33,41%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>80</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>55054</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>45487</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>65085</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>45645</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>65881</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>30,77%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>25,42%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>36,37%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>53373</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>44020</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>62642</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>28,68%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>23,65%</t>
+          <t>25,51%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>33,66%</t>
+          <t>36,82%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>94706</t>
+          <t>94700</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>122000</t>
+          <t>123574</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,7 +1730,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>33,42%</t>
+          <t>33,85%</t>
         </is>
       </c>
     </row>
@@ -1743,72 +1743,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>25974</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>19528</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>34479</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>13,96%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>10,49%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>18,53%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>16216</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>10266</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>22351</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>10821</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>23528</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>9,06%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>5,74%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>12,49%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>25974</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>18970</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>34706</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>13,96%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,65%</t>
+          <t>13,15%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>33130</t>
+          <t>33574</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>52092</t>
+          <t>52806</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>14,47%</t>
         </is>
       </c>
     </row>
@@ -1856,72 +1856,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>42540</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>33728</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>51278</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>22,86%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>18,12%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>27,55%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>39</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>26514</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>19795</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>35153</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>19701</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>34721</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>14,82%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>11,06%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>19,65%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>42540</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>33226</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>51285</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>22,86%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>27,56%</t>
+          <t>19,4%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>57299</t>
+          <t>56290</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>82331</t>
+          <t>79600</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>15,7%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>22,55%</t>
+          <t>21,81%</t>
         </is>
       </c>
     </row>
@@ -1969,57 +1969,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>280</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>186097</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>186097</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>186097</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>264</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>178935</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>178935</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>178935</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>280</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>186097</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>186097</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>186097</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2086,72 +2086,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>42009</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>32638</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>52940</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>13,63%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>10,59%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>17,18%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>90</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>61144</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>50092</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>72302</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>51105</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>73773</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>21,04%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>17,23%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>24,88%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>42009</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>33178</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>52684</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>13,63%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>17,58%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>17,09%</t>
+          <t>25,38%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>87430</t>
+          <t>89226</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>118267</t>
+          <t>119680</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>14,9%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>19,75%</t>
+          <t>19,98%</t>
         </is>
       </c>
     </row>
@@ -2199,72 +2199,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>47060</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>37549</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>57571</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>15,27%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>12,18%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>18,68%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>83</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>55373</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>45697</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>66560</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>44128</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>65385</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>19,05%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>15,72%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>22,9%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>47060</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>37244</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>57769</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>15,27%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>15,18%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>22,5%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>88796</t>
+          <t>88518</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>117461</t>
+          <t>118264</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>14,78%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>19,61%</t>
+          <t>19,75%</t>
         </is>
       </c>
     </row>
@@ -2312,72 +2312,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>138</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>92384</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>79791</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>105579</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>29,97%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>25,89%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>34,25%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>139</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>93912</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>82497</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>106066</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>81886</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>108939</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>32,31%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>28,38%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>36,49%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>138</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>92384</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>80025</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>105533</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>29,97%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>25,96%</t>
+          <t>28,17%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>34,24%</t>
+          <t>37,48%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>168323</t>
+          <t>166756</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>203814</t>
+          <t>203014</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>28,11%</t>
+          <t>27,84%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>34,03%</t>
+          <t>33,9%</t>
         </is>
       </c>
     </row>
@@ -2425,72 +2425,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>49053</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>38991</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>59393</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>15,91%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>12,65%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>19,27%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>45</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>29294</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>22024</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>38148</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>21828</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>37412</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>10,08%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>7,58%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>13,13%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>49053</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>39308</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>59497</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>15,91%</t>
-        </is>
-      </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>19,3%</t>
+          <t>12,87%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>65180</t>
+          <t>66519</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>91277</t>
+          <t>92945</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>15,52%</t>
         </is>
       </c>
     </row>
@@ -2538,72 +2538,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>77719</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>66109</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>90237</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>25,21%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>21,45%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>29,28%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>75</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>50923</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>40856</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>62037</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>41017</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>61574</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>17,52%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>14,06%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>21,34%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>119</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>77719</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>65032</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>89033</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>25,21%</t>
-        </is>
-      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>21,1%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>28,89%</t>
+          <t>21,19%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>112741</t>
+          <t>113208</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>144704</t>
+          <t>146979</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>18,83%</t>
+          <t>18,9%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>24,16%</t>
+          <t>24,54%</t>
         </is>
       </c>
     </row>
@@ -2651,57 +2651,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>464</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>308226</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>308226</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>308226</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>432</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>290646</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>290646</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>290646</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>464</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>308226</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>308226</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>308226</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2813,13 +2813,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de preocuparse por su aspecto en 2012 (tasa de respuesta: 95,52%)</t>
+          <t>Menores según la frecuencia de preocuparse por su aspecto, percibida por el/la menor [KIDSCREEN 20] en 2012 (tasa de respuesta: 95,52%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2830,7 +2830,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2998,72 +2998,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>16911</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>11171</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>23953</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>10,88%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>7,19%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>15,41%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>48</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>33776</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>25799</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>42820</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>25774</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>43029</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>22,52%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>17,2%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>28,55%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>16911</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>11193</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>23601</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>10,88%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>17,19%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,18%</t>
+          <t>28,69%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>40517</t>
+          <t>41000</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>61361</t>
+          <t>62930</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>20,09%</t>
+          <t>20,61%</t>
         </is>
       </c>
     </row>
@@ -3111,72 +3111,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>22666</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>16519</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>30565</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>14,58%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>10,63%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>19,67%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>26427</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>18933</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>35125</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>18730</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>34884</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>17,62%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>12,62%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>23,42%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>22666</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>16401</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>30531</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>14,58%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>19,64%</t>
+          <t>23,26%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3191,12 +3191,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>39713</t>
+          <t>39511</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>59268</t>
+          <t>61114</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>19,41%</t>
+          <t>20,01%</t>
         </is>
       </c>
     </row>
@@ -3224,72 +3224,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>42337</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>33835</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>52704</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>27,24%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>21,77%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>33,91%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>51</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>36338</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>28109</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>45204</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>28471</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>45486</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>24,23%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>18,74%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>30,14%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>42337</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>34254</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>51866</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>27,24%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>22,04%</t>
+          <t>18,99%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>33,37%</t>
+          <t>30,33%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3304,12 +3304,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>66718</t>
+          <t>65259</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>91804</t>
+          <t>91239</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3319,12 +3319,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>21,85%</t>
+          <t>21,37%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>30,06%</t>
+          <t>29,88%</t>
         </is>
       </c>
     </row>
@@ -3337,72 +3337,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>28151</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>20948</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>37410</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>18,11%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>13,48%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>24,07%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>31</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>21347</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>15245</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>28854</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>14491</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>29002</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>14,23%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>10,17%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>19,24%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>28151</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>21095</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>36643</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>18,11%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>23,58%</t>
+          <t>19,34%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3417,12 +3417,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>39372</t>
+          <t>39819</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>61548</t>
+          <t>61256</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3432,12 +3432,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>13,04%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>20,15%</t>
+          <t>20,06%</t>
         </is>
       </c>
     </row>
@@ -3450,72 +3450,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>45361</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>36533</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>55193</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>29,19%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>23,5%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>35,51%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>47</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>32077</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>24606</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>40477</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>23800</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>40760</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>21,39%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>16,41%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>26,99%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>45361</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>36498</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>55644</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>29,19%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>23,48%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>35,8%</t>
+          <t>27,18%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>65839</t>
+          <t>65366</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>90726</t>
+          <t>90136</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>21,4%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>29,71%</t>
+          <t>29,51%</t>
         </is>
       </c>
     </row>
@@ -3563,57 +3563,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>223</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>155427</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>155427</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>155427</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>214</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>149965</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>149965</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>149965</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>223</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>155427</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>155427</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>155427</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3680,72 +3680,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>40766</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>32665</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>50242</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>23,99%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>19,22%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>29,56%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>61</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>44786</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>35406</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>54771</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>35994</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>54677</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>27,7%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>21,9%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>33,87%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>40766</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>32254</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>50911</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>23,99%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>22,26%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>29,95%</t>
+          <t>33,82%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3760,12 +3760,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>72575</t>
+          <t>74358</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>97566</t>
+          <t>99592</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3775,12 +3775,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>21,88%</t>
+          <t>22,42%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>29,42%</t>
+          <t>30,03%</t>
         </is>
       </c>
     </row>
@@ -3793,107 +3793,107 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>20307</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>14340</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>27696</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>11,95%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>8,44%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>16,3%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>49</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>34316</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>26200</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>43142</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>26372</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>43008</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>21,22%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>16,2%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>26,68%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>20307</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>13701</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>27985</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>11,95%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>16,31%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
+          <t>26,6%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>54623</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>44544</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>67933</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
           <t>16,47%</t>
         </is>
       </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>54623</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>45005</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>67387</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>16,47%</t>
-        </is>
-      </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>20,32%</t>
+          <t>20,48%</t>
         </is>
       </c>
     </row>
@@ -3906,72 +3906,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>52565</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>42348</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>61389</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>30,93%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>24,92%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>36,12%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>65</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>46075</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>36323</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>56229</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>36743</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>55935</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>28,5%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>22,46%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>34,78%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>52565</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>42474</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>61876</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>30,93%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>24,99%</t>
+          <t>22,72%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>36,41%</t>
+          <t>34,59%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -3986,12 +3986,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>85101</t>
+          <t>85138</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>112649</t>
+          <t>111951</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4001,12 +4001,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>25,66%</t>
+          <t>25,67%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>33,97%</t>
+          <t>33,76%</t>
         </is>
       </c>
     </row>
@@ -4019,72 +4019,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>29084</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>21437</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>38516</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>17,11%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>12,61%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>22,66%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>19605</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>13282</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>27030</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>13523</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>27638</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>12,13%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>8,21%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>16,72%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>29084</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>21741</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>37664</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>17,11%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>22,16%</t>
+          <t>17,09%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4099,12 +4099,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>39342</t>
+          <t>38070</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>60388</t>
+          <t>58275</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4114,12 +4114,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,21%</t>
+          <t>17,57%</t>
         </is>
       </c>
     </row>
@@ -4132,72 +4132,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>27238</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>20000</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>35992</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>16,03%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>11,77%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>21,18%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>16906</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>11386</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>23984</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>11338</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>24314</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>10,46%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>7,04%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>14,83%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>27238</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>19802</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>35684</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>16,03%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>21,0%</t>
+          <t>15,04%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>34853</t>
+          <t>35159</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>54088</t>
+          <t>55762</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>16,31%</t>
+          <t>16,81%</t>
         </is>
       </c>
     </row>
@@ -4245,57 +4245,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>169960</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>169960</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>169960</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>229</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>161688</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>161688</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>161688</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>169960</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>169960</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>169960</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4362,72 +4362,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>57677</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>48105</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>69436</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>17,73%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>14,78%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>21,34%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>109</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>78562</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>66021</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>93830</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>66196</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>92488</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>25,21%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>21,18%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>30,11%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>57677</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>47963</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>70143</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>17,73%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>21,24%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>29,68%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4442,12 +4442,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>119733</t>
+          <t>119882</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>154032</t>
+          <t>155918</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4457,12 +4457,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>18,82%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>24,18%</t>
+          <t>24,48%</t>
         </is>
       </c>
     </row>
@@ -4475,72 +4475,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>42973</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>33854</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>53997</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>13,21%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>10,4%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>16,59%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>86</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>60743</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>50178</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>72721</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>49748</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>73880</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>19,49%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>16,1%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>23,33%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>42973</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>34550</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>54001</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>13,21%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>15,96%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>23,71%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4555,12 +4555,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>88489</t>
+          <t>89767</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>119497</t>
+          <t>119849</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4570,12 +4570,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>14,09%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>18,81%</t>
         </is>
       </c>
     </row>
@@ -4588,72 +4588,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>138</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>94903</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>81175</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>109145</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>29,17%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>24,95%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>33,54%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>116</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>82413</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>70012</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>96293</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>70010</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>95399</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>26,44%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="O18" s="2" t="inlineStr">
         <is>
           <t>22,46%</t>
         </is>
       </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>30,9%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>138</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>94903</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>83259</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>108346</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>29,17%</t>
-        </is>
-      </c>
-      <c r="O18" s="2" t="inlineStr">
-        <is>
-          <t>25,59%</t>
-        </is>
-      </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>30,61%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>159318</t>
+          <t>156861</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>194896</t>
+          <t>195564</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4683,12 +4683,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>25,01%</t>
+          <t>24,62%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>30,59%</t>
+          <t>30,7%</t>
         </is>
       </c>
     </row>
@@ -4701,72 +4701,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>57235</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>45931</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>70179</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>17,59%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>14,12%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>21,57%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>59</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>40952</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>31563</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>51908</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>32162</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>52392</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>13,14%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>10,13%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>16,66%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>57235</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>45642</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>68929</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>17,59%</t>
-        </is>
-      </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>21,18%</t>
+          <t>16,81%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -4781,12 +4781,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>84170</t>
+          <t>83211</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>114899</t>
+          <t>113418</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -4796,12 +4796,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>13,06%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>18,04%</t>
+          <t>17,8%</t>
         </is>
       </c>
     </row>
@@ -4814,72 +4814,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>72599</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>61086</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>85435</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>22,31%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>18,77%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>26,26%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>73</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>48983</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>39197</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>61487</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>38974</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>60341</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>15,72%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>12,58%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>19,73%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>103</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>72599</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>61223</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>85366</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>22,31%</t>
-        </is>
-      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>12,51%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>26,24%</t>
+          <t>19,36%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -4894,12 +4894,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>106102</t>
+          <t>105594</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>137342</t>
+          <t>139197</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>16,58%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>21,85%</t>
         </is>
       </c>
     </row>
@@ -4927,57 +4927,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>473</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>325387</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>325387</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>325387</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>443</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>311653</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>311653</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>311653</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>473</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>325387</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>325387</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>325387</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5089,13 +5089,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de preocuparse por su aspecto en 2016 (tasa de respuesta: 95,57%)</t>
+          <t>Menores según la frecuencia de preocuparse por su aspecto, percibida por el/la menor [KIDSCREEN 20] en 2016 (tasa de respuesta: 95,57%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -5106,7 +5106,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -5274,72 +5274,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>25060</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>18617</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>34427</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>14,03%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>10,42%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>19,27%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>44</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>31334</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>23770</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>41228</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>23440</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>40572</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>17,46%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>13,24%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>22,97%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>25060</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>18431</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>33249</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>14,03%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>13,06%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>18,62%</t>
+          <t>22,61%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5354,12 +5354,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>45527</t>
+          <t>45941</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>68613</t>
+          <t>69183</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5369,12 +5369,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,83%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>19,16%</t>
+          <t>19,32%</t>
         </is>
       </c>
     </row>
@@ -5387,72 +5387,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>31579</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>24239</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>41937</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>17,68%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>13,57%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>23,48%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>40</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>29075</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>21051</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>38226</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>21878</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>38295</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>16,2%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>11,73%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>21,3%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>31579</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>23720</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>41260</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>17,68%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>23,1%</t>
+          <t>21,34%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5467,12 +5467,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>49524</t>
+          <t>49953</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>74911</t>
+          <t>73174</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5482,12 +5482,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>13,95%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>20,92%</t>
+          <t>20,43%</t>
         </is>
       </c>
     </row>
@@ -5500,72 +5500,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>34626</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>26754</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>44284</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>19,39%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>14,98%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>24,79%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>65</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>45113</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>36468</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>54172</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>36050</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>54900</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>25,14%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>20,32%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>30,18%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>34626</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>26809</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>43257</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>19,39%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>20,09%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>24,22%</t>
+          <t>30,59%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5580,12 +5580,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>67407</t>
+          <t>67013</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>93721</t>
+          <t>93430</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5595,12 +5595,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>18,71%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>26,17%</t>
+          <t>26,09%</t>
         </is>
       </c>
     </row>
@@ -5613,72 +5613,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>38030</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>29566</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>48589</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>21,29%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>16,55%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>27,2%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>43</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>29468</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>22016</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>38601</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>21383</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>37843</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>16,42%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>12,27%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>21,51%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>38030</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>29259</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>47707</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>21,29%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16,38%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>26,71%</t>
+          <t>21,09%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5693,12 +5693,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>56025</t>
+          <t>55306</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>78716</t>
+          <t>80736</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5708,12 +5708,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>15,45%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>21,98%</t>
+          <t>22,55%</t>
         </is>
       </c>
     </row>
@@ -5726,72 +5726,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>49316</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>38718</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>59441</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>27,61%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>21,68%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>33,28%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>65</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>44480</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>35288</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>53942</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>35697</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>54558</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>24,78%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>19,66%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>30,06%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>49316</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>39923</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>59712</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>27,61%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>22,35%</t>
+          <t>19,89%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>33,43%</t>
+          <t>30,4%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>80713</t>
+          <t>80832</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>109222</t>
+          <t>107955</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>22,57%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>30,5%</t>
+          <t>30,15%</t>
         </is>
       </c>
     </row>
@@ -5839,57 +5839,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>178611</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>178611</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>178611</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>257</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>179470</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>179470</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>179470</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>178611</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>178611</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>178611</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5956,72 +5956,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>25998</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>18932</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>35049</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>15,24%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>11,1%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>20,55%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>59</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>43113</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>34680</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>54029</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>34353</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>53333</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>26,16%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>21,04%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>32,78%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>25998</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>18865</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>35718</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>15,24%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>20,84%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20,94%</t>
+          <t>32,36%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6036,12 +6036,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>56928</t>
+          <t>56641</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>82023</t>
+          <t>83196</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>16,89%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>24,46%</t>
+          <t>24,81%</t>
         </is>
       </c>
     </row>
@@ -6069,72 +6069,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>35643</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>27254</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>45336</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>20,89%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>15,98%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>26,58%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>46</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>30662</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>23249</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>40027</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>22949</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>40054</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>18,6%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>14,11%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>24,29%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>35643</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>27329</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>45295</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>20,89%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>13,92%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>26,55%</t>
+          <t>24,3%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>55027</t>
+          <t>54501</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>79183</t>
+          <t>79896</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>16,25%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>23,61%</t>
+          <t>23,82%</t>
         </is>
       </c>
     </row>
@@ -6182,72 +6182,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>40768</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>32131</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>51660</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>23,9%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>18,83%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>30,28%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>66</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>46261</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>36024</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>56672</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>36473</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>55828</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>28,07%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>21,86%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>34,39%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>40768</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>32148</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>50512</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>23,9%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>22,13%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>29,61%</t>
+          <t>33,87%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>73048</t>
+          <t>73738</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>100428</t>
+          <t>101127</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>21,99%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>29,94%</t>
+          <t>30,15%</t>
         </is>
       </c>
     </row>
@@ -6295,72 +6295,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>35034</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>26718</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>44318</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>20,54%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>15,66%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>25,98%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>21884</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>15239</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>29951</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>15370</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>30365</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>13,28%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>9,25%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>18,17%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>35034</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>26440</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>45083</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>20,54%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>26,43%</t>
+          <t>18,42%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6375,12 +6375,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>47037</t>
+          <t>46648</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>69911</t>
+          <t>69357</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6390,12 +6390,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>13,91%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>20,84%</t>
+          <t>20,68%</t>
         </is>
       </c>
     </row>
@@ -6408,72 +6408,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>33150</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>25549</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>42672</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>19,43%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>14,98%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>25,01%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>22887</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>16709</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>31209</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>15964</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>31586</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>13,89%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>10,14%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>18,94%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>33150</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>24990</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>42733</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>19,43%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>25,05%</t>
+          <t>19,17%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6488,12 +6488,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>44750</t>
+          <t>45192</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>68320</t>
+          <t>67848</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6503,12 +6503,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>20,37%</t>
+          <t>20,23%</t>
         </is>
       </c>
     </row>
@@ -6521,57 +6521,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>170592</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>170592</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>170592</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>234</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>164807</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>164807</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>164807</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>230</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>170592</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>170592</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>170592</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6638,72 +6638,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>51057</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>40753</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>63056</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>14,62%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>11,67%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>18,06%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>103</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>74447</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>61523</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>88199</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>63398</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>88523</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>21,62%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>17,87%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>25,62%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>51057</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>40935</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>63405</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>14,62%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>18,41%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>25,71%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6718,12 +6718,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>108640</t>
+          <t>108581</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>141586</t>
+          <t>141448</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6733,12 +6733,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>15,66%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>20,4%</t>
         </is>
       </c>
     </row>
@@ -6751,72 +6751,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>67222</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>55290</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>80368</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>19,25%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>15,83%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>23,01%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>86</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>59737</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>48488</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>72062</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>49689</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>71986</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>17,35%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>14,08%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>20,93%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>67222</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>56280</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>81468</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>19,25%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>23,33%</t>
+          <t>20,91%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>111458</t>
+          <t>111388</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>145195</t>
+          <t>145057</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6846,12 +6846,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>16,06%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>20,94%</t>
+          <t>20,92%</t>
         </is>
       </c>
     </row>
@@ -6864,72 +6864,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>75394</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>63605</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>89629</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>21,59%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>18,21%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>25,67%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>131</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>91375</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>77774</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>104460</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>78239</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>104795</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>26,54%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>22,59%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>30,34%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>104</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>75394</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>62884</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>88763</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>21,59%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>18,01%</t>
+          <t>22,73%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>25,42%</t>
+          <t>30,44%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>148549</t>
+          <t>149141</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>184676</t>
+          <t>185061</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6959,12 +6959,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>21,42%</t>
+          <t>21,51%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>26,63%</t>
+          <t>26,69%</t>
         </is>
       </c>
     </row>
@@ -6977,72 +6977,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>73064</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>60096</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>85318</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>20,92%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>17,21%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>24,43%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>73</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>51352</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>40784</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>62702</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>41169</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>62980</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>14,92%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>11,85%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>18,21%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>73064</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>60399</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>85051</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>20,92%</t>
-        </is>
-      </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>24,36%</t>
+          <t>18,29%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7057,12 +7057,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>107913</t>
+          <t>108653</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>141249</t>
+          <t>141991</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7072,12 +7072,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>15,67%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>20,37%</t>
+          <t>20,48%</t>
         </is>
       </c>
     </row>
@@ -7090,72 +7090,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>82467</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>69784</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>97226</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>23,62%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>19,98%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>27,84%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>98</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>67367</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>57390</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>80557</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>56048</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>80815</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>19,57%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>16,67%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>23,4%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>115</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>82467</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>69703</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>96024</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>23,62%</t>
-        </is>
-      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>19,96%</t>
+          <t>16,28%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>27,5%</t>
+          <t>23,47%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7170,12 +7170,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>133267</t>
+          <t>131767</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>168721</t>
+          <t>166029</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7185,12 +7185,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>19,22%</t>
+          <t>19,0%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>24,33%</t>
+          <t>23,94%</t>
         </is>
       </c>
     </row>
@@ -7203,57 +7203,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>480</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>349203</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>349203</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>349203</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>491</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>344278</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>344278</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>344278</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>480</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>349203</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>349203</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>349203</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
